--- a/data/trans_orig/P16A15-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A15-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98260</t>
+          <t>97865</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>134419</t>
+          <t>137904</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>178535</t>
+          <t>177276</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>229140</t>
+          <t>228612</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>287101</t>
+          <t>287072</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>354996</t>
+          <t>351147</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>897304</t>
+          <t>893819</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>933463</t>
+          <t>933858</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1085973</t>
+          <t>1086501</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1136578</t>
+          <t>1137837</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1991839</t>
+          <t>1995688</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2059734</t>
+          <t>2059763</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40220</t>
+          <t>41527</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70013</t>
+          <t>70845</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39314</t>
+          <t>40150</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68938</t>
+          <t>70549</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86349</t>
+          <t>87406</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>128030</t>
+          <t>129325</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1622381</t>
+          <t>1621549</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1652174</t>
+          <t>1650867</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1518735</t>
+          <t>1517124</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1548359</t>
+          <t>1547523</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3152037</t>
+          <t>3150742</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3193718</t>
+          <t>3192661</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12661</t>
+          <t>11885</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30553</t>
+          <t>30564</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20028</t>
+          <t>19589</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21149</t>
+          <t>21284</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44746</t>
+          <t>44545</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>520855</t>
+          <t>520844</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>538747</t>
+          <t>539523</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>456384</t>
+          <t>456823</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>470401</t>
+          <t>470519</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>983074</t>
+          <t>983275</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1006671</t>
+          <t>1006536</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>164412</t>
+          <t>164340</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>217366</t>
+          <t>218178</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>238111</t>
+          <t>235995</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>297241</t>
+          <t>297745</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>413344</t>
+          <t>420869</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>500464</t>
+          <t>502330</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3058159</t>
+          <t>3057347</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3111113</t>
+          <t>3111185</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3081956</t>
+          <t>3081452</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3141086</t>
+          <t>3143202</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6154258</t>
+          <t>6152392</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6241378</t>
+          <t>6233853</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,68%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2012 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>179519</t>
+          <t>179935</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>232769</t>
+          <t>230355</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>295418</t>
+          <t>294338</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>357737</t>
+          <t>358142</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>491868</t>
+          <t>491334</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>576098</t>
+          <t>570908</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>741874</t>
+          <t>744288</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>795124</t>
+          <t>794708</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>974761</t>
+          <t>974356</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1037080</t>
+          <t>1038160</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1731043</t>
+          <t>1736233</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1815273</t>
+          <t>1815807</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,7%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96868</t>
+          <t>94725</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>141479</t>
+          <t>138324</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72922</t>
+          <t>72993</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>111752</t>
+          <t>114633</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>180366</t>
+          <t>179038</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>238384</t>
+          <t>240425</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1817731</t>
+          <t>1820886</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1862342</t>
+          <t>1864485</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1640097</t>
+          <t>1637216</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1678927</t>
+          <t>1678856</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3472675</t>
+          <t>3470634</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3530693</t>
+          <t>3532021</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22136</t>
+          <t>21056</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49507</t>
+          <t>46643</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9328</t>
+          <t>9640</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27269</t>
+          <t>27481</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34579</t>
+          <t>36026</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65336</t>
+          <t>66872</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>430825</t>
+          <t>433689</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>458196</t>
+          <t>459276</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>430385</t>
+          <t>430173</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>448326</t>
+          <t>448014</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>872650</t>
+          <t>871114</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>903407</t>
+          <t>901960</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>313078</t>
+          <t>314818</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>389609</t>
+          <t>390895</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>396748</t>
+          <t>396812</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>478160</t>
+          <t>481977</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>731729</t>
+          <t>741186</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>841260</t>
+          <t>846611</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3024575</t>
+          <t>3023289</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3101106</t>
+          <t>3099366</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3063841</t>
+          <t>3060024</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3145253</t>
+          <t>3145189</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6114925</t>
+          <t>6109574</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6224456</t>
+          <t>6214999</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,34%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>136190</t>
+          <t>136157</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>178191</t>
+          <t>179076</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>216265</t>
+          <t>217632</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>273089</t>
+          <t>274203</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>365091</t>
+          <t>367290</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>438180</t>
+          <t>439261</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>576156</t>
+          <t>575271</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>618157</t>
+          <t>618190</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>721571</t>
+          <t>720457</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>778395</t>
+          <t>777028</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1310827</t>
+          <t>1309746</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1383916</t>
+          <t>1381717</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,0%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>112272</t>
+          <t>114035</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>156580</t>
+          <t>157455</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>104965</t>
+          <t>107286</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>150893</t>
+          <t>152530</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>228184</t>
+          <t>232468</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>293788</t>
+          <t>296538</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1919805</t>
+          <t>1918930</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1964113</t>
+          <t>1962350</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1837407</t>
+          <t>1835770</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1883335</t>
+          <t>1881014</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3770897</t>
+          <t>3768147</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3836501</t>
+          <t>3832217</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,28%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17324</t>
+          <t>17422</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39289</t>
+          <t>40392</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>9162</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27817</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30060</t>
+          <t>30973</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58162</t>
+          <t>58836</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>507597</t>
+          <t>506494</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>529562</t>
+          <t>529464</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>521323</t>
+          <t>520467</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>540559</t>
+          <t>539978</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1037865</t>
+          <t>1037191</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1065967</t>
+          <t>1065054</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>281457</t>
+          <t>283691</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>352983</t>
+          <t>352219</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>354548</t>
+          <t>352046</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>432771</t>
+          <t>430903</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>655373</t>
+          <t>655392</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>755921</t>
+          <t>756046</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3024635</t>
+          <t>3025399</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3096161</t>
+          <t>3093927</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3099329</t>
+          <t>3101197</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3177552</t>
+          <t>3180054</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6153797</t>
+          <t>6153672</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6254345</t>
+          <t>6254326</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,51%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas en 2023 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>106521</t>
+          <t>106008</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>139726</t>
+          <t>138626</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>212655</t>
+          <t>212310</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>250445</t>
+          <t>247691</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>328551</t>
+          <t>326402</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>376467</t>
+          <t>376858</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,77%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>374216</t>
+          <t>375316</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>407421</t>
+          <t>407934</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>501617</t>
+          <t>504371</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>539407</t>
+          <t>539752</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>889537</t>
+          <t>889146</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>937453</t>
+          <t>939602</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,22%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>146676</t>
+          <t>147280</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>251505</t>
+          <t>251146</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>193926</t>
+          <t>193387</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>912898</t>
+          <t>900023</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>399152</t>
+          <t>398265</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1233283</t>
+          <t>1175496</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>25,96%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2038822</t>
+          <t>2039181</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2143651</t>
+          <t>2143047</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1324247</t>
+          <t>1337122</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2043219</t>
+          <t>2043758</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3294189</t>
+          <t>3351976</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4128320</t>
+          <t>4129207</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,2%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46395</t>
+          <t>45238</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72920</t>
+          <t>71487</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49020</t>
+          <t>48852</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71571</t>
+          <t>72017</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>101349</t>
+          <t>99977</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135938</t>
+          <t>135008</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>573703</t>
+          <t>575136</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>600228</t>
+          <t>601385</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>588892</t>
+          <t>588446</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>611443</t>
+          <t>611611</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1171148</t>
+          <t>1172078</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1205737</t>
+          <t>1207109</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,35%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>308155</t>
+          <t>308974</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>442600</t>
+          <t>441809</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>486674</t>
+          <t>489185</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1176976</t>
+          <t>1238434</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>873872</t>
+          <t>871597</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1735370</t>
+          <t>1839774</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3008292</t>
+          <t>3009083</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3142737</t>
+          <t>3141918</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2472694</t>
+          <t>2411236</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3162996</t>
+          <t>3160485</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5365192</t>
+          <t>5260788</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6226690</t>
+          <t>6228965</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,72%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A15-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A15-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>97865</t>
+          <t>97750</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>137904</t>
+          <t>139075</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>177276</t>
+          <t>179219</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>228612</t>
+          <t>231051</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>287072</t>
+          <t>287398</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>351147</t>
+          <t>352162</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>893819</t>
+          <t>892648</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>933858</t>
+          <t>933973</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1086501</t>
+          <t>1084062</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1137837</t>
+          <t>1135894</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1995688</t>
+          <t>1994673</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2059763</t>
+          <t>2059437</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,75%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41527</t>
+          <t>40634</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70845</t>
+          <t>70581</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40150</t>
+          <t>39306</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70549</t>
+          <t>69467</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87406</t>
+          <t>85947</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>129325</t>
+          <t>128012</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1621549</t>
+          <t>1621813</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1650867</t>
+          <t>1651760</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1517124</t>
+          <t>1518206</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1547523</t>
+          <t>1548367</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3150742</t>
+          <t>3152055</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3192661</t>
+          <t>3194120</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11885</t>
+          <t>12933</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30564</t>
+          <t>30828</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>5929</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19589</t>
+          <t>19411</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21284</t>
+          <t>21814</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44545</t>
+          <t>42975</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>520844</t>
+          <t>520580</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>539523</t>
+          <t>538475</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>456823</t>
+          <t>457001</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>470519</t>
+          <t>470483</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>983275</t>
+          <t>984845</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1006536</t>
+          <t>1006006</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>164340</t>
+          <t>164565</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>218178</t>
+          <t>216536</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>235995</t>
+          <t>236389</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>297745</t>
+          <t>297601</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>420869</t>
+          <t>419808</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>502330</t>
+          <t>496259</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3057347</t>
+          <t>3058989</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3111185</t>
+          <t>3110960</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3081452</t>
+          <t>3081596</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3143202</t>
+          <t>3142808</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6152392</t>
+          <t>6158463</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6233853</t>
+          <t>6234914</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>179935</t>
+          <t>179888</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>230355</t>
+          <t>228528</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>294338</t>
+          <t>293499</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>358142</t>
+          <t>357697</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>491334</t>
+          <t>491833</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>570908</t>
+          <t>574065</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>744288</t>
+          <t>746115</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>794708</t>
+          <t>794755</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>974356</t>
+          <t>974801</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1038160</t>
+          <t>1038999</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1736233</t>
+          <t>1733076</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1815807</t>
+          <t>1815308</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,68%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94725</t>
+          <t>93699</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>138324</t>
+          <t>138755</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72993</t>
+          <t>73794</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114633</t>
+          <t>113337</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>179038</t>
+          <t>180317</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>240425</t>
+          <t>240398</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1820886</t>
+          <t>1820455</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1864485</t>
+          <t>1865511</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1637216</t>
+          <t>1638512</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1678856</t>
+          <t>1678055</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3470634</t>
+          <t>3470661</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3532021</t>
+          <t>3530742</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21056</t>
+          <t>21907</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46643</t>
+          <t>47202</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9640</t>
+          <t>9365</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27481</t>
+          <t>27212</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36026</t>
+          <t>33536</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66872</t>
+          <t>65202</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>433689</t>
+          <t>433130</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>459276</t>
+          <t>458425</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>430173</t>
+          <t>430442</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>448014</t>
+          <t>448289</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>871114</t>
+          <t>872784</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>901960</t>
+          <t>904450</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>314818</t>
+          <t>316328</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>390895</t>
+          <t>388797</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>396812</t>
+          <t>396492</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>481977</t>
+          <t>476944</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>741186</t>
+          <t>731998</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>846611</t>
+          <t>839881</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3023289</t>
+          <t>3025387</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3099366</t>
+          <t>3097856</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3060024</t>
+          <t>3065057</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3145189</t>
+          <t>3145509</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6109574</t>
+          <t>6116304</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6214999</t>
+          <t>6224187</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,48%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>136157</t>
+          <t>134299</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>179076</t>
+          <t>178566</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>217632</t>
+          <t>215314</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>274203</t>
+          <t>272400</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>367290</t>
+          <t>365071</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>439261</t>
+          <t>437883</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>575271</t>
+          <t>575781</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>618190</t>
+          <t>620048</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>720457</t>
+          <t>722260</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>777028</t>
+          <t>779346</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1309746</t>
+          <t>1311124</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1381717</t>
+          <t>1383936</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>79,13%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>114035</t>
+          <t>111740</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>157455</t>
+          <t>158566</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>107286</t>
+          <t>106071</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>152530</t>
+          <t>153405</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>232468</t>
+          <t>231695</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>296538</t>
+          <t>298504</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1918930</t>
+          <t>1917819</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1962350</t>
+          <t>1964645</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1835770</t>
+          <t>1834895</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1881014</t>
+          <t>1882229</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3768147</t>
+          <t>3766181</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3832217</t>
+          <t>3832990</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17422</t>
+          <t>17108</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40392</t>
+          <t>38413</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9162</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28673</t>
+          <t>27038</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30973</t>
+          <t>30500</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58836</t>
+          <t>58763</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>506494</t>
+          <t>508473</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>529464</t>
+          <t>529778</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>520467</t>
+          <t>522102</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>539978</t>
+          <t>540922</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1037191</t>
+          <t>1037264</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1065054</t>
+          <t>1065527</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>283691</t>
+          <t>285355</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>352219</t>
+          <t>353971</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>352046</t>
+          <t>349796</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>430903</t>
+          <t>429451</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>655392</t>
+          <t>654641</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>756046</t>
+          <t>758025</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3025399</t>
+          <t>3023647</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3093927</t>
+          <t>3092263</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3101197</t>
+          <t>3102649</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3180054</t>
+          <t>3182304</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6153672</t>
+          <t>6151693</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6254326</t>
+          <t>6255077</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>122507</t>
+          <t>127900</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>106008</t>
+          <t>109408</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>138626</t>
+          <t>145599</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>229759</t>
+          <t>250670</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>212310</t>
+          <t>230645</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>247691</t>
+          <t>271010</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>352266</t>
+          <t>378570</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>326402</t>
+          <t>352383</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>376858</t>
+          <t>406018</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,05%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>391435</t>
+          <t>449642</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>375316</t>
+          <t>431943</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>407934</t>
+          <t>468134</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>522303</t>
+          <t>569446</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>504371</t>
+          <t>549106</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>539752</t>
+          <t>589471</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>913738</t>
+          <t>1019088</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>889146</t>
+          <t>991640</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>939602</t>
+          <t>1045275</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,79%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>752062</t>
+          <t>820116</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>752062</t>
+          <t>820116</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>752062</t>
+          <t>820116</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1266004</t>
+          <t>1397658</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1266004</t>
+          <t>1397658</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1266004</t>
+          <t>1397658</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>215004</t>
+          <t>230825</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>147280</t>
+          <t>205531</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>251146</t>
+          <t>259567</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>388742</t>
+          <t>199857</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>193387</t>
+          <t>180856</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>900023</t>
+          <t>223091</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>603746</t>
+          <t>430682</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>398265</t>
+          <t>397368</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1175496</t>
+          <t>463089</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2075323</t>
+          <t>1999741</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2039181</t>
+          <t>1970999</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2143047</t>
+          <t>2025035</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1848403</t>
+          <t>1970850</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1337122</t>
+          <t>1947616</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2043758</t>
+          <t>1989851</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3923726</t>
+          <t>3970592</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3351976</t>
+          <t>3938185</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4129207</t>
+          <t>4003906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>90,97%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>57795</t>
+          <t>64160</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45238</t>
+          <t>51525</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71487</t>
+          <t>79276</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>59907</t>
+          <t>67802</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48852</t>
+          <t>56430</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72017</t>
+          <t>81394</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>117702</t>
+          <t>131963</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>99977</t>
+          <t>114961</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135008</t>
+          <t>153200</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>588828</t>
+          <t>647427</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>575136</t>
+          <t>632311</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>601385</t>
+          <t>660062</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>600556</t>
+          <t>667075</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>588446</t>
+          <t>653483</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>611611</t>
+          <t>678447</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1189384</t>
+          <t>1314501</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1172078</t>
+          <t>1293264</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1207109</t>
+          <t>1331503</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,05%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>395306</t>
+          <t>422886</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>308974</t>
+          <t>390869</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>441809</t>
+          <t>461618</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>678408</t>
+          <t>518329</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>489185</t>
+          <t>485388</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1238434</t>
+          <t>550491</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1073714</t>
+          <t>941215</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>871597</t>
+          <t>890502</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1839774</t>
+          <t>989872</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>13,66%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3055586</t>
+          <t>3096809</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3009083</t>
+          <t>3058077</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3141918</t>
+          <t>3128826</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2971262</t>
+          <t>3207372</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2411236</t>
+          <t>3175210</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3160485</t>
+          <t>3240313</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6026848</t>
+          <t>6304181</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5260788</t>
+          <t>6255524</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6228965</t>
+          <t>6354894</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,71%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3450892</t>
+          <t>3519695</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3450892</t>
+          <t>3519695</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3450892</t>
+          <t>3519695</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3649670</t>
+          <t>3725701</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3649670</t>
+          <t>3725701</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3649670</t>
+          <t>3725701</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7100562</t>
+          <t>7245396</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7100562</t>
+          <t>7245396</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7100562</t>
+          <t>7245396</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
